--- a/data/trans_orig/P79A6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A6_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>61190</t>
+          <t>68133</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>59039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67233</t>
+          <t>74324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>96081</t>
+          <t>109680</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88592</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101833</t>
+          <t>115119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>157271</t>
+          <t>177813</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147128</t>
+          <t>166575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165662</t>
+          <t>187349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24492</t>
+          <t>28242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32508</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>27567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>48341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76695</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>113084</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113084</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>113084</t>
+          <t>128273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>214916</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>147560</t>
+          <t>174930</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136991</t>
+          <t>164379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154346</t>
+          <t>182461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>142404</t>
+          <t>165473</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>127665</t>
+          <t>150850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152901</t>
+          <t>175652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>289964</t>
+          <t>340404</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>274421</t>
+          <t>321918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>304235</t>
+          <t>353900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,22 +1216,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30326</t>
+          <t>32953</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45065</t>
+          <t>47576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>45092</t>
+          <t>52094</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>38598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60635</t>
+          <t>70580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>162326</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>162326</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162326</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>172730</t>
+          <t>198426</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172730</t>
+          <t>198426</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>172730</t>
+          <t>198426</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>335056</t>
+          <t>392498</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>335056</t>
+          <t>392498</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335056</t>
+          <t>392498</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>21770</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21889</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29921</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24014</t>
+          <t>28944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>10211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11260</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>220010</t>
+          <t>256037</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207996</t>
+          <t>242453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229921</t>
+          <t>266812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>257146</t>
+          <t>296924</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238496</t>
+          <t>279280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>270105</t>
+          <t>310830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>477156</t>
+          <t>552961</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>455883</t>
+          <t>533348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>493374</t>
+          <t>569764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70549</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65952</t>
+          <t>77678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>114094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
